--- a/artfynd/A 34043-2024 artfynd.xlsx
+++ b/artfynd/A 34043-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150743</v>
+        <v>121150744</v>
       </c>
       <c r="B4" t="n">
-        <v>91957</v>
+        <v>89380</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739311</v>
+        <v>739305</v>
       </c>
       <c r="R4" t="n">
-        <v>7209117</v>
+        <v>7209130</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1023,7 +1023,7 @@
         <v>121150742</v>
       </c>
       <c r="B5" t="n">
-        <v>91963</v>
+        <v>91973</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150744</v>
+        <v>121150743</v>
       </c>
       <c r="B6" t="n">
-        <v>89370</v>
+        <v>91967</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739305</v>
+        <v>739311</v>
       </c>
       <c r="R6" t="n">
-        <v>7209130</v>
+        <v>7209117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 34043-2024 artfynd.xlsx
+++ b/artfynd/A 34043-2024 artfynd.xlsx
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150742</v>
+        <v>121150743</v>
       </c>
       <c r="B5" t="n">
-        <v>91973</v>
+        <v>91967</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739308</v>
+        <v>739311</v>
       </c>
       <c r="R5" t="n">
-        <v>7209112</v>
+        <v>7209117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150743</v>
+        <v>121150742</v>
       </c>
       <c r="B6" t="n">
-        <v>91967</v>
+        <v>91973</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739311</v>
+        <v>739308</v>
       </c>
       <c r="R6" t="n">
-        <v>7209117</v>
+        <v>7209112</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 34043-2024 artfynd.xlsx
+++ b/artfynd/A 34043-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150744</v>
+        <v>121150742</v>
       </c>
       <c r="B4" t="n">
-        <v>89380</v>
+        <v>91985</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739305</v>
+        <v>739308</v>
       </c>
       <c r="R4" t="n">
-        <v>7209130</v>
+        <v>7209112</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150743</v>
+        <v>121150744</v>
       </c>
       <c r="B5" t="n">
-        <v>91967</v>
+        <v>89387</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739311</v>
+        <v>739305</v>
       </c>
       <c r="R5" t="n">
-        <v>7209117</v>
+        <v>7209130</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150742</v>
+        <v>121150743</v>
       </c>
       <c r="B6" t="n">
-        <v>91973</v>
+        <v>91979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739308</v>
+        <v>739311</v>
       </c>
       <c r="R6" t="n">
-        <v>7209112</v>
+        <v>7209117</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 34043-2024 artfynd.xlsx
+++ b/artfynd/A 34043-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150742</v>
+        <v>121150744</v>
       </c>
       <c r="B4" t="n">
-        <v>91985</v>
+        <v>89388</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>6276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739308</v>
+        <v>739305</v>
       </c>
       <c r="R4" t="n">
-        <v>7209112</v>
+        <v>7209130</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150744</v>
+        <v>121150743</v>
       </c>
       <c r="B5" t="n">
-        <v>89387</v>
+        <v>91980</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739305</v>
+        <v>739311</v>
       </c>
       <c r="R5" t="n">
-        <v>7209130</v>
+        <v>7209117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1131,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121150743</v>
+        <v>121150742</v>
       </c>
       <c r="B6" t="n">
-        <v>91979</v>
+        <v>91986</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1143,25 +1143,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1175,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>739311</v>
+        <v>739308</v>
       </c>
       <c r="R6" t="n">
-        <v>7209117</v>
+        <v>7209112</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 34043-2024 artfynd.xlsx
+++ b/artfynd/A 34043-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150744</v>
+        <v>121150743</v>
       </c>
       <c r="B4" t="n">
-        <v>89388</v>
+        <v>91983</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739305</v>
+        <v>739311</v>
       </c>
       <c r="R4" t="n">
-        <v>7209130</v>
+        <v>7209117</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150743</v>
+        <v>121150744</v>
       </c>
       <c r="B5" t="n">
-        <v>91980</v>
+        <v>89391</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739311</v>
+        <v>739305</v>
       </c>
       <c r="R5" t="n">
-        <v>7209117</v>
+        <v>7209130</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1134,7 +1134,7 @@
         <v>121150742</v>
       </c>
       <c r="B6" t="n">
-        <v>91986</v>
+        <v>91989</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 34043-2024 artfynd.xlsx
+++ b/artfynd/A 34043-2024 artfynd.xlsx
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150743</v>
+        <v>121150744</v>
       </c>
       <c r="B4" t="n">
-        <v>91983</v>
+        <v>89391</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +921,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>739311</v>
+        <v>739305</v>
       </c>
       <c r="R4" t="n">
-        <v>7209117</v>
+        <v>7209130</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1020,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121150744</v>
+        <v>121150743</v>
       </c>
       <c r="B5" t="n">
-        <v>89391</v>
+        <v>91983</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,25 +1032,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1064,10 +1064,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>739305</v>
+        <v>739311</v>
       </c>
       <c r="R5" t="n">
-        <v>7209130</v>
+        <v>7209117</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
